--- a/daily/2026-04-09.xlsx
+++ b/daily/2026-04-09.xlsx
@@ -32,7 +32,7 @@
       <color rgb="00E0E0E0"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -42,6 +42,21 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001E1E2E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EF4444"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0022C55E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F59E0B"/>
       </patternFill>
     </fill>
   </fills>
@@ -57,7 +72,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -65,6 +80,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -710,7 +728,6 @@
       <c r="V3" t="n">
         <v>11</v>
       </c>
-      <c r="W3" t="inlineStr"/>
       <c r="X3" t="n">
         <v>-0.3</v>
       </c>
@@ -1116,7 +1133,6 @@
       <c r="V8" t="n">
         <v>1</v>
       </c>
-      <c r="W8" t="inlineStr"/>
       <c r="X8" t="n">
         <v>-46.8</v>
       </c>
@@ -3490,7 +3506,6 @@
       <c r="V37" t="n">
         <v>13</v>
       </c>
-      <c r="W37" t="inlineStr"/>
       <c r="X37" t="n">
         <v>19.2</v>
       </c>
@@ -3814,7 +3829,6 @@
       <c r="V41" t="n">
         <v>13</v>
       </c>
-      <c r="W41" t="inlineStr"/>
       <c r="X41" t="n">
         <v>0</v>
       </c>
@@ -3974,7 +3988,6 @@
       <c r="V43" t="n">
         <v>13</v>
       </c>
-      <c r="W43" t="inlineStr"/>
       <c r="X43" t="n">
         <v>-3.5</v>
       </c>
@@ -4052,7 +4065,6 @@
       <c r="V44" t="n">
         <v>22</v>
       </c>
-      <c r="W44" t="inlineStr"/>
       <c r="X44" t="n">
         <v>-0.3</v>
       </c>
@@ -4212,7 +4224,6 @@
       <c r="V46" t="n">
         <v>22</v>
       </c>
-      <c r="W46" t="inlineStr"/>
       <c r="X46" t="n">
         <v>1.3</v>
       </c>
@@ -4372,7 +4383,6 @@
       <c r="V48" t="n">
         <v>23</v>
       </c>
-      <c r="W48" t="inlineStr"/>
       <c r="X48" t="n">
         <v>12.6</v>
       </c>
@@ -4450,7 +4460,6 @@
       <c r="V49" t="n">
         <v>22</v>
       </c>
-      <c r="W49" t="inlineStr"/>
       <c r="X49" t="n">
         <v>-4.8</v>
       </c>
@@ -4610,7 +4619,6 @@
       <c r="V51" t="n">
         <v>22</v>
       </c>
-      <c r="W51" t="inlineStr"/>
       <c r="X51" t="n">
         <v>10.5</v>
       </c>
@@ -4688,7 +4696,6 @@
       <c r="V52" t="n">
         <v>23</v>
       </c>
-      <c r="W52" t="inlineStr"/>
       <c r="X52" t="n">
         <v>-12.8</v>
       </c>
@@ -4930,7 +4937,6 @@
       <c r="V55" t="n">
         <v>22</v>
       </c>
-      <c r="W55" t="inlineStr"/>
       <c r="X55" t="n">
         <v>25.1</v>
       </c>
@@ -5008,7 +5014,6 @@
       <c r="V56" t="n">
         <v>23</v>
       </c>
-      <c r="W56" t="inlineStr"/>
       <c r="X56" t="n">
         <v>37.6</v>
       </c>
@@ -5086,7 +5091,6 @@
       <c r="V57" t="n">
         <v>22</v>
       </c>
-      <c r="W57" t="inlineStr"/>
       <c r="X57" t="n">
         <v>-7.5</v>
       </c>
@@ -5656,7 +5660,6 @@
       <c r="V64" t="n">
         <v>21</v>
       </c>
-      <c r="W64" t="inlineStr"/>
       <c r="X64" t="n">
         <v>-16.1</v>
       </c>
@@ -9091,1303 +9094,2969 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Collin Sexton</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>CHI @ WAS</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="3" t="n">
         <v>21.5</v>
       </c>
+      <c r="E2" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Sexton scored 27 pts vs 21.5 line (+5.5), UNDER missed by 5.5 pts. Sexton played 34 min (+7.5 vs L10 avg of 26.8) — 28% more than expected. Shooting efficiency was hot: 57.1% FG (+12.0% vs L10 avg of 45.1%). 12/21 from the field. Counter-signals that proved correct: Trend, Defense, Pace, Min Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 13.1 pts — actual 27 was 13.9 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-10 10:23</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>Tre Jones</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>CHI @ WAS</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>LEAN OVER</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="4" t="n">
         <v>18.5</v>
       </c>
+      <c r="E3" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Jones scored 31 pts vs 18.5 line (+12.5), OVER hit by 12.5 pts. Minutes were as expected: 30 played vs L10 avg 27.8. Shooting was in line with averages: 64.3% FG (9/14, L10 avg 59.5%). Signals that called it correctly: HR L10, Trend, Defense, Pace, FG Trend (6/10 aligned). Counter-signals that were wrong: Volume, HR L30, Context. Projection model targeted 18.6 pts — actual 31 was 12.4 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Jones's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-10 10:23</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>Guerschon Yabusele</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>CHI @ WAS</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="4" t="n">
         <v>12.5</v>
       </c>
+      <c r="E4" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Yabusele scored 5 pts vs 12.5 line (-7.5), UNDER hit by 7.5 pts. Yabusele played 16 min (-8.2 vs L10 avg of 24.4) — 34% less than expected. Shooting efficiency was hot: 50.0% FG (+9.2% vs L10 avg of 40.8%). 2/4 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Context (4/10 aligned). Counter-signals that were wrong: Trend, Defense, H2H. Projection model targeted 10.9 pts — actual 5 was 5.9 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Yabusele's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-10 10:23</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Leonard Miller</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>CHI @ WAS</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="3" t="n">
         <v>16.5</v>
       </c>
+      <c r="E5" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Miller scored 26 pts vs 16.5 line (+9.5), UNDER missed by 9.5 pts. Miller played 39 min (+14.9 vs L10 avg of 23.8) — 63% more than expected. Shooting efficiency was hot: 78.6% FG (+27.6% vs L10 avg of 51.0%). 11/14 from the field. Counter-signals that proved correct: Trend, Defense, Pace, FG Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 8.1 pts — actual 26 was 17.9 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-10 10:23</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Anthony Gill</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>CHI @ WAS</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="3" t="n">
         <v>11.5</v>
       </c>
+      <c r="E6" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Gill scored 14 pts vs 11.5 line (+2.5), UNDER missed by 2.5 pts. Gill played 39 min (+11.0 vs L10 avg of 27.9) — 39% more than expected. Shooting efficiency was cold: 42.9% FG (-28.8% vs L10 avg of 71.7%). 3/7 from the field. Counter-signals that proved correct: HR L10, Trend, Defense, Pace. Signals that were wrong: Volume, HR L30, Context. Projection model targeted 8.6 pts — actual 14 was 5.4 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-10 10:23</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Rob Dillingham</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>CHI @ WAS</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="4" t="n">
         <v>14.5</v>
       </c>
+      <c r="E7" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Dillingham scored 5 pts vs 14.5 line (-9.5), UNDER hit by 9.5 pts. Dillingham played 27 min (+6.6 vs L10 avg of 20.7) — 32% more than expected. Shooting efficiency was cold: 20.0% FG (-25.3% vs L10 avg of 45.3%). 2/10 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Context, H2H (5/10 aligned). Counter-signals that were wrong: Trend, Defense, Pace. Projection model targeted 13.3 pts — actual 5 was 8.3 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Dillingham's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-10 10:23</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>Will Riley</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>CHI @ WAS</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="3" t="n">
         <v>22.5</v>
       </c>
+      <c r="E8" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Riley scored 23 pts vs 22.5 line (+0.5), UNDER missed by 0.5 pts. Riley played 38 min (+7.5 vs L10 avg of 30.4) — 25% more than expected. Shooting efficiency was cold: 36.4% FG (-11.5% vs L10 avg of 47.9%). 8/22 from the field. Counter-signals that proved correct: Trend, Defense, H2H, Pace. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 7.4 pts — actual 23 was 15.6 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-10 10:23</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>Brandon Ingram</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>MIA @ TOR</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="3" t="n">
         <v>20.5</v>
       </c>
+      <c r="E9" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Ingram scored 38 pts vs 20.5 line (+17.5), UNDER missed by 17.5 pts. Ingram played 37 min (+4.9 vs L10 avg of 31.7) — 15% more than expected. Shooting efficiency was hot: 56.5% FG (+5.6% vs L10 avg of 50.9%). 13/23 from the field. Counter-signals that proved correct: Volume, Defense, H2H, Pace. Signals that were wrong: HR L30, HR L10, Trend. Projection model targeted 19.8 pts — actual 38 was 18.2 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-10 10:23</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>Tyler Herro</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>MIA @ TOR</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="4" t="n">
         <v>20.5</v>
       </c>
+      <c r="E10" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Herro scored 15 pts vs 20.5 line (-5.5), UNDER hit by 5.5 pts. Herro played 28 min (-5.7 vs L10 avg of 33.9) — 17% less than expected. Shooting was in line with averages: 50.0% FG (6/12, L10 avg 47.3%). Signals that called it correctly: HR L10, Trend, Context, Defense, Pace (6/10 aligned). Counter-signals that were wrong: Volume, HR L30, H2H. Projection model targeted 20.1 pts — actual 15 was 5.1 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Herro's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-10 10:23</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>RJ Barrett</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>MIA @ TOR</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="4" t="n">
         <v>20.5</v>
       </c>
+      <c r="E11" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Barrett scored 22 pts vs 20.5 line (+1.5), OVER hit by 1.5 pts. Barrett played 35 min (+4.9 vs L10 avg of 30.1) — 16% more than expected. Shooting efficiency was cold: 40.0% FG (-9.5% vs L10 avg of 49.5%). 6/15 from the field. Signals that called it correctly: Trend, Defense, H2H, Pace, FG Trend (5/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 22.9 pts — actual 22 was 0.9 pts close (correct direction). Result classification: CLOSE_CALL. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Barrett in this role.</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-10 10:23</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>Bam Adebayo</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>MIA @ TOR</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="3" t="n">
         <v>19.5</v>
       </c>
+      <c r="E12" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Adebayo scored 24 pts vs 19.5 line (+4.5), UNDER missed by 4.5 pts. Minutes were as expected: 38 played vs L10 avg 34.9. Shooting efficiency was hot: 64.3% FG (+26.0% vs L10 avg of 38.3%). 9/14 from the field. Counter-signals that proved correct: Volume, HR L30, Context, Min Trend. Signals that were wrong: HR L10, Trend, Defense. Projection model targeted 18.0 pts — actual 24 was 6.0 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-10 10:23</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Scottie Barnes</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>MIA @ TOR</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" s="3" t="n">
         <v>17.5</v>
       </c>
+      <c r="E13" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Barnes scored 13 pts vs 17.5 line (-4.5), OVER missed by 4.5 pts. Barnes played 25 min (-4.7 vs L10 avg of 29.7) — 16% less than expected. Shooting efficiency was hot: 66.7% FG (+10.0% vs L10 avg of 56.7%). 4/6 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, Trend. Signals that were wrong: Defense, H2H, Pace. Projection model targeted 18.1 pts — actual 13 was 5.1 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Barnes for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-10 10:23</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Norman Powell</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>MIA @ TOR</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" s="4" t="n">
         <v>16.5</v>
       </c>
+      <c r="E14" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Powell scored 7 pts vs 16.5 line (-9.5), UNDER hit by 9.5 pts. Powell played 17 min (-10.9 vs L10 avg of 27.5) — 40% less than expected. Shooting was in line with averages: 40.0% FG (2/5, L10 avg 44.8%). Signals that called it correctly: Trend, Defense, Pace, FG Trend, Min Trend (5/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 15.2 pts — actual 7 was 8.2 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Powell's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-10 10:23</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>Andrew Wiggins</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>MIA @ TOR</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D15" t="n">
+      <c r="D15" s="3" t="n">
         <v>14.5</v>
       </c>
+      <c r="E15" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Wiggins scored 5 pts vs 14.5 line (-9.5), OVER missed by 9.5 pts. Wiggins played 22 min (-6.2 vs L10 avg of 27.8) — 22% less than expected. Shooting efficiency was cold: 33.3% FG (-19.9% vs L10 avg of 53.2%). 2/6 from the field. Counter-signals that proved correct: HR L30, HR L10, Defense, Pace. Signals that were wrong: Volume, Trend, Context. Projection model targeted 15.4 pts — actual 5 was 10.4 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Wiggins for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-10 10:23</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Immanuel Quickley</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>MIA @ TOR</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D16" t="n">
+      <c r="D16" s="4" t="n">
         <v>13.5</v>
       </c>
+      <c r="E16" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Quickley scored 11 pts vs 13.5 line (-2.5), UNDER hit by 2.5 pts. Quickley played 23 min (-7.2 vs L10 avg of 30.4) — 24% less than expected. Shooting was in line with averages: 40.0% FG (4/10, L10 avg 40.0%). Signals that called it correctly: HR L10, Trend, FG Trend, Min Trend (4/10 aligned). Counter-signals that were wrong: Volume, HR L30, Context. Projection model targeted 11.3 pts — actual 11 was 0.3 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Quickley in this role.</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-10 10:23</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>Jaime Jaquez Jr.</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>MIA @ TOR</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D17" t="n">
+      <c r="D17" s="4" t="n">
         <v>11.5</v>
       </c>
+      <c r="E17" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Jr. scored 15 pts vs 11.5 line (+3.5), OVER hit by 3.5 pts. Minutes were as expected: 24 played vs L10 avg 25.5. Shooting efficiency was hot: 66.7% FG (+16.4% vs L10 avg of 50.3%). 6/9 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (6/10 aligned). Counter-signals that were wrong: Defense, H2H, Pace. Projection model targeted 13.4 pts — actual 15 was 1.6 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Jr. in this role.</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-10 10:23</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>Jakob Poeltl</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>MIA @ TOR</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D18" t="n">
+      <c r="D18" s="3" t="n">
         <v>10.5</v>
       </c>
+      <c r="E18" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Poeltl scored 6 pts vs 10.5 line (-4.5), OVER missed by 4.5 pts. Poeltl played 17 min (-7.4 vs L10 avg of 24.8) — 30% less than expected. Shooting efficiency was hot: 75.0% FG (+12.2% vs L10 avg of 62.8%). 3/4 from the field. Counter-signals that proved correct: HR L30, Defense, FG Trend, Min Trend. Signals that were wrong: Volume, HR L10, Trend. Projection model targeted 13.0 pts — actual 6 was 7.0 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Poeltl for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-10 10:23</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>Pelle Larsson</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>MIA @ TOR</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>LEAN OVER</t>
         </is>
       </c>
-      <c r="D19" t="n">
+      <c r="D19" s="3" t="n">
         <v>10.5</v>
       </c>
+      <c r="E19" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Larsson scored 10 pts vs 10.5 line (-0.5), OVER missed by 0.5 pts. Minutes were as expected: 32 played vs L10 avg 30.7. Shooting efficiency was cold: 40.0% FG (-10.0% vs L10 avg of 50.0%). 4/10 from the field. Counter-signals that proved correct: Defense, H2H, Pace. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 10.4 pts — actual 10 was 0.4 pts close (wrong direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-10 10:23</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>Sandro Mamukelashvili</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>MIA @ TOR</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D20" t="n">
+      <c r="D20" s="3" t="n">
         <v>9.5</v>
       </c>
+      <c r="E20" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Mamukelashvili scored 5 pts vs 9.5 line (-4.5), OVER missed by 4.5 pts. Mamukelashvili played 18 min (-4.5 vs L10 avg of 23.0) — 20% less than expected. Shooting efficiency was cold: 33.3% FG (-19.8% vs L10 avg of 53.1%). 2/6 from the field. All 10 agreeing signals (Volume, HR L30, HR L10, Trend) were wrong — result went directly against the consensus. Projection model targeted 12.9 pts — actual 5 was 7.9 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Mamukelashvili for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-10 10:23</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>Davion Mitchell</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>MIA @ TOR</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D21" t="n">
+      <c r="D21" s="4" t="n">
         <v>8.5</v>
       </c>
+      <c r="E21" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Mitchell scored 15 pts vs 8.5 line (+6.5), OVER hit by 6.5 pts. Mitchell played 37 min (+7.1 vs L10 avg of 30.2) — 24% more than expected. Shooting efficiency was hot: 77.8% FG (+29.9% vs L10 avg of 47.9%). 7/9 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (7/10 aligned). Counter-signals that were wrong: Defense, Pace, FG Trend. Projection model targeted 10.4 pts — actual 15 was 4.6 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Mitchell's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-10 10:23</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>Ja'Kobe Walter</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>MIA @ TOR</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D22" t="n">
+      <c r="D22" s="3" t="n">
         <v>7.5</v>
       </c>
+      <c r="E22" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Walter scored 7 pts vs 7.5 line (-0.5), OVER missed by 0.5 pts. Minutes were as expected: 25 played vs L10 avg 27.6. Shooting efficiency was cold: 40.0% FG (-11.9% vs L10 avg of 51.9%). 2/5 from the field. Counter-signals that proved correct: Trend, H2H. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 8.2 pts — actual 7 was 1.2 pts close (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-10 10:23</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>Jamal Shead</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>MIA @ TOR</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D23" t="n">
+      <c r="D23" s="3" t="n">
         <v>5.5</v>
       </c>
+      <c r="E23" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Shead scored 8 pts vs 5.5 line (+2.5), UNDER missed by 2.5 pts. Shead played 22 min (-5.2 vs L10 avg of 26.9) — 19% less than expected. Shooting efficiency was hot: 50.0% FG (+13.6% vs L10 avg of 36.4%). 3/6 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, Trend. Signals that were wrong: Context, H2H. Projection model targeted 4.9 pts — actual 8 was 3.1 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Shead for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-10 10:23</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>Collin Murray-Boyles</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>MIA @ TOR</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D24" t="n">
+      <c r="D24" s="3" t="n">
         <v>9.5</v>
       </c>
+      <c r="E24" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Murray-Boyles scored 17 pts vs 9.5 line (+7.5), UNDER missed by 7.5 pts. Minutes were as expected: 22 played vs L10 avg 20.9. Shooting efficiency was hot: 100.0% FG (+37.7% vs L10 avg of 62.3%). 7/7 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, Trend. Signals that were wrong: Context, H2H, Min Trend. Projection model targeted 7.5 pts — actual 17 was 9.5 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-10 10:23</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>Jayson Tatum</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>BOS @ NYK</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D25" t="n">
+      <c r="D25" s="3" t="n">
         <v>25.5</v>
       </c>
+      <c r="E25" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Tatum scored 24 pts vs 25.5 line (-1.5), OVER missed by 1.5 pts. Tatum played 40 min (+6.1 vs L10 avg of 33.7) — 18% more than expected. Shooting efficiency was cold: 31.8% FG (-10.6% vs L10 avg of 42.4%). 7/22 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, Context. Signals that were wrong: Trend, H2H. Projection model targeted 29.0 pts — actual 24 was 5.0 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-10 10:23</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>Jalen Brunson</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>BOS @ NYK</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D26" t="n">
+      <c r="D26" s="3" t="n">
         <v>24.5</v>
       </c>
+      <c r="E26" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Brunson scored 25 pts vs 24.5 line (+0.5), UNDER missed by 0.5 pts. Minutes were as expected: 37 played vs L10 avg 36.4. Shooting efficiency was hot: 52.6% FG (+6.8% vs L10 avg of 45.8%). 10/19 from the field. Counter-signals that proved correct: HR L30, HR L10, H2H, FG Trend. Signals that were wrong: Volume, Trend, Context. Projection model targeted 23.1 pts — actual 25 was 1.9 pts close (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-10 10:23</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>Karl-Anthony Towns</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>BOS @ NYK</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D27" t="n">
+      <c r="D27" s="4" t="n">
         <v>17.5</v>
       </c>
+      <c r="E27" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Towns scored 16 pts vs 17.5 line (-1.5), UNDER hit by 1.5 pts. Minutes were as expected: 30 played vs L10 avg 29.4. Shooting efficiency was cold: 50.0% FG (-6.2% vs L10 avg of 56.2%). 6/12 from the field. Signals that called it correctly: Trend, Defense, Pace, FG Trend, Min Trend (5/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 17.2 pts — actual 16 was 1.2 pts close (correct direction). Result classification: CLOSE_CALL. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Towns in this role.</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-10 10:23</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>Derrick White</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>BOS @ NYK</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D28" t="n">
+      <c r="D28" s="4" t="n">
         <v>17.5</v>
       </c>
+      <c r="E28" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>WIN — White scored 8 pts vs 17.5 line (-9.5), UNDER hit by 9.5 pts. White played 38 min (+3.2 vs L10 avg of 34.3) — 9% more than expected. Shooting efficiency was cold: 20.0% FG (-27.2% vs L10 avg of 47.2%). 2/10 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (8/10 aligned). Counter-signals that were wrong: H2H, FG Trend. Projection model targeted 16.5 pts — actual 8 was 8.5 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Strong signal alignment (8/10) with confirmed result — this player/matchup pattern is reliable for future predictions.</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-10 10:23</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>Payton Pritchard</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>BOS @ NYK</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D29" t="n">
+      <c r="D29" s="3" t="n">
         <v>16.5</v>
       </c>
+      <c r="E29" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Pritchard scored 23 pts vs 16.5 line (+6.5), UNDER missed by 6.5 pts. Pritchard played 36 min (+4.8 vs L10 avg of 30.7) — 16% more than expected. Shooting was in line with averages: 50.0% FG (10/20, L10 avg 49.8%). Counter-signals that proved correct: Volume, HR L30, FG Trend. Signals that were wrong: HR L10, Trend, Context. Projection model targeted 9.5 pts — actual 23 was 13.5 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-10 10:23</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="4" t="inlineStr">
         <is>
           <t>OG Anunoby</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="4" t="inlineStr">
         <is>
           <t>BOS @ NYK</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D30" t="n">
+      <c r="D30" s="4" t="n">
         <v>16.5</v>
       </c>
+      <c r="E30" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Anunoby scored 13 pts vs 16.5 line (-3.5), UNDER hit by 3.5 pts. Minutes were as expected: 36 played vs L10 avg 35.0. Shooting efficiency was cold: 40.0% FG (-9.0% vs L10 avg of 49.0%). 4/10 from the field. Signals that called it correctly: Defense, H2H, Pace, FG Trend (4/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 9.3 pts — actual 13 was 3.7 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Anunoby's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-10 10:23</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>Mikal Bridges</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>BOS @ NYK</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D31" t="n">
+      <c r="D31" s="3" t="n">
         <v>12.5</v>
       </c>
+      <c r="E31" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Bridges scored 10 pts vs 12.5 line (-2.5), OVER missed by 2.5 pts. Minutes were as expected: 31 played vs L10 avg 32.6. Shooting efficiency was hot: 100.0% FG (+50.1% vs L10 avg of 49.9%). 4/4 from the field. Counter-signals that proved correct: HR L30, Defense, Pace. Signals that were wrong: Volume, HR L10, Trend. Projection model targeted 12.9 pts — actual 10 was 2.9 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-10 10:23</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>Josh Hart</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>BOS @ NYK</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D32" t="n">
+      <c r="D32" s="4" t="n">
         <v>10.5</v>
       </c>
+      <c r="E32" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Hart scored 26 pts vs 10.5 line (+15.5), OVER hit by 15.5 pts. Hart played 34 min (+3.7 vs L10 avg of 30.8) — 12% more than expected. Shooting efficiency was hot: 66.7% FG (+12.7% vs L10 avg of 54.0%). 10/15 from the field. Signals that called it correctly: Volume, HR L30, Context, H2H, FG Trend (6/10 aligned). Counter-signals that were wrong: HR L10, Trend, Defense. Projection model targeted 12.0 pts — actual 26 was 14.0 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Hart's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-10 10:23</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>Neemias Queta</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>BOS @ NYK</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>LEAN OVER</t>
         </is>
       </c>
-      <c r="D33" t="n">
+      <c r="D33" s="4" t="n">
         <v>9.5</v>
       </c>
+      <c r="E33" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Queta scored 10 pts vs 9.5 line (+0.5), OVER hit by 0.5 pts. Queta played 24 min (-3.9 vs L10 avg of 28.1) — 14% less than expected. Shooting efficiency was cold: 66.7% FG (-8.3% vs L10 avg of 75.0%). 4/6 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (7/10 aligned). Counter-signals that were wrong: Defense, H2H, Pace. Projection model targeted 9.4 pts — actual 10 was 0.6 pts close (wrong direction). Result classification: CLOSE_CALL. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Queta in this role.</t>
+        </is>
+      </c>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-10 10:23</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="4" t="inlineStr">
         <is>
           <t>Nikola Vučević</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>BOS @ NYK</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D34" t="n">
+      <c r="D34" s="4" t="n">
         <v>9.5</v>
       </c>
+      <c r="E34" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Vučević scored 10 pts vs 9.5 line (+0.5), OVER hit by 0.5 pts. Vučević played 24 min (+4.8 vs L10 avg of 19.0) — 25% more than expected. Shooting efficiency was hot: 57.1% FG (+22.8% vs L10 avg of 34.3%). 4/7 from the field. Signals that called it correctly: Volume, HR L30, Context, H2H (4/10 aligned). Counter-signals that were wrong: HR L10, Trend, Defense. Projection model targeted 13.2 pts — actual 10 was 3.2 pts off (correct direction). Result classification: CLOSE_CALL. Note: Result confirms Vučević's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-10 10:23</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>Sam Hauser</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>BOS @ NYK</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>LEAN UNDER</t>
         </is>
       </c>
-      <c r="D35" t="n">
+      <c r="D35" s="4" t="n">
         <v>8.5</v>
       </c>
+      <c r="E35" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Hauser scored 6 pts vs 8.5 line (-2.5), UNDER hit by 2.5 pts. Hauser played 32 min (+6.5 vs L10 avg of 25.0) — 26% more than expected. Shooting efficiency was cold: 28.6% FG (-15.6% vs L10 avg of 44.2%). 2/7 from the field. Signals that called it correctly: HR L30, HR L10, Context, Defense, Pace (6/10 aligned). Counter-signals that were wrong: Volume, Trend, H2H. Projection model targeted 8.4 pts — actual 6 was 2.4 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Hauser's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-10 10:23</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="3" t="inlineStr">
         <is>
           <t>Baylor Scheierman</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="3" t="inlineStr">
         <is>
           <t>BOS @ NYK</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D36" t="n">
+      <c r="D36" s="3" t="n">
         <v>6.5</v>
       </c>
+      <c r="E36" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Scheierman scored 20 pts vs 6.5 line (+13.5), UNDER missed by 13.5 pts. Scheierman played 30 min (+8.4 vs L10 avg of 22.0) — 38% more than expected. Shooting efficiency was hot: 87.5% FG (+44.7% vs L10 avg of 42.8%). 7/8 from the field. Counter-signals that proved correct: Volume, HR L30, Context. Signals that were wrong: HR L10, Trend, Defense. Projection model targeted 1.8 pts — actual 20 was 18.2 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-10 10:23</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>Ben Saraf</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="3" t="inlineStr">
         <is>
           <t>IND @ BKN</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D37" t="n">
+      <c r="D37" s="3" t="n">
         <v>15.5</v>
       </c>
+      <c r="E37" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Saraf scored 19 pts vs 15.5 line (+3.5), UNDER missed by 3.5 pts. Minutes were as expected: 28 played vs L10 avg 25.7. Shooting efficiency was hot: 50.0% FG (+12.9% vs L10 avg of 37.1%). 8/16 from the field. Counter-signals that proved correct: Trend, Defense, H2H, Pace. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 9.7 pts — actual 19 was 9.3 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-10 10:23</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="3" t="inlineStr">
         <is>
           <t>Jay Huff</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="3" t="inlineStr">
         <is>
           <t>IND @ BKN</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D38" t="n">
+      <c r="D38" s="3" t="n">
         <v>11.5</v>
       </c>
+      <c r="E38" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Huff scored 14 pts vs 11.5 line (+2.5), UNDER missed by 2.5 pts. Minutes were as expected: 25 played vs L10 avg 21.9. Shooting efficiency was hot: 100.0% FG (+48.7% vs L10 avg of 51.3%). 6/6 from the field. Counter-signals that proved correct: Defense, FG Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 10.3 pts — actual 14 was 3.7 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-10 10:23</t>
+        </is>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="4" t="inlineStr">
         <is>
           <t>Jarace Walker</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>IND @ BKN</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D39" t="n">
+      <c r="D39" s="4" t="n">
         <v>16.5</v>
       </c>
+      <c r="E39" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Walker scored 14 pts vs 16.5 line (-2.5), UNDER hit by 2.5 pts. Minutes were as expected: 30 played vs L10 avg 28.9. Shooting efficiency was cold: 33.3% FG (-17.9% vs L10 avg of 51.2%). 5/15 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (8/10 aligned). Counter-signals that were wrong: Defense, FG Trend. Projection model targeted 9.3 pts — actual 14 was 4.7 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Strong signal alignment (8/10) with confirmed result — this player/matchup pattern is reliable for future predictions.</t>
+        </is>
+      </c>
+      <c r="I39" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-10 10:23</t>
+        </is>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="5" t="inlineStr">
         <is>
           <t>Kobe Brown</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B40" s="5" t="inlineStr">
         <is>
           <t>IND @ BKN</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C40" s="5" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D40" t="n">
+      <c r="D40" s="5" t="n">
         <v>9.5</v>
       </c>
+      <c r="E40" s="5" t="n"/>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="n"/>
+      <c r="H40" s="5" t="inlineStr"/>
+      <c r="I40" s="5" t="n"/>
+      <c r="J40" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-10 10:23</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="4" t="inlineStr">
         <is>
           <t>Malachi Smith</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>IND @ BKN</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D41" t="n">
+      <c r="D41" s="4" t="n">
         <v>14.5</v>
       </c>
+      <c r="E41" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Smith scored 11 pts vs 14.5 line (-3.5), UNDER hit by 3.5 pts. Smith played 40 min (+19.7 vs L10 avg of 20.5) — 96% more than expected. Shooting efficiency was cold: 30.8% FG (-20.3% vs L10 avg of 51.1%). 4/13 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (5/10 aligned). Counter-signals that were wrong: Defense, H2H, Pace. Projection model targeted 6.5 pts — actual 11 was 4.5 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Smith's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I41" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-10 10:23</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="4" t="inlineStr">
         <is>
           <t>Quenton Jackson</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B42" s="4" t="inlineStr">
         <is>
           <t>IND @ BKN</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C42" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D42" t="n">
+      <c r="D42" s="4" t="n">
         <v>13.5</v>
       </c>
+      <c r="E42" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Jackson scored 12 pts vs 13.5 line (-1.5), UNDER hit by 1.5 pts. Jackson played 26 min (+7.3 vs L10 avg of 19.0) — 38% more than expected. Shooting was in line with averages: 45.5% FG (5/11, L10 avg 49.4%). Signals that called it correctly: Volume, HR L30, HR L10, Context, H2H (6/10 aligned). Counter-signals that were wrong: Trend, Defense, FG Trend. Projection model targeted 4.3 pts — actual 12 was 7.7 pts off (correct direction). Result classification: CLOSE_CALL. Note: Result confirms Jackson's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I42" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-10 10:23</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="4" t="inlineStr">
         <is>
           <t>Drake Powell</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>IND @ BKN</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C43" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D43" t="n">
+      <c r="D43" s="4" t="n">
         <v>13.5</v>
       </c>
+      <c r="E43" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="n">
+        <v>-11.5</v>
+      </c>
+      <c r="H43" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Powell scored 2 pts vs 13.5 line (-11.5), UNDER hit by 11.5 pts. Powell played 20 min (-7.9 vs L10 avg of 28.0) — 28% less than expected. Shooting efficiency was cold: 14.3% FG (-26.8% vs L10 avg of 41.1%). 1/7 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Context (4/10 aligned). Counter-signals that were wrong: Trend, Defense, H2H. Projection model targeted 4.0 pts — actual 2 was 2.0 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Powell in this role.</t>
+        </is>
+      </c>
+      <c r="I43" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-10 10:23</t>
+        </is>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="3" t="inlineStr">
         <is>
           <t>Tyrese Maxey</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B44" s="3" t="inlineStr">
         <is>
           <t>PHI @ HOU</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C44" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D44" t="n">
+      <c r="D44" s="3" t="n">
         <v>28.5</v>
       </c>
+      <c r="E44" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Maxey scored 23 pts vs 28.5 line (-5.5), OVER missed by 5.5 pts. Maxey played 33 min (-4.0 vs L10 avg of 37.3) — 11% less than expected. Shooting was in line with averages: 45.0% FG (9/20, L10 avg 45.7%). Counter-signals that proved correct: Volume, HR L30, HR L10, Trend. Signals that were wrong: FG Trend, Min Trend. Projection model targeted 33.9 pts — actual 23 was 10.9 pts off (correct direction). Loss classification: MODEL_FAILURE. Note: Model signals were misleading for this matchup — review Maxey's recent role and usage for pattern shifts.</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_FAILURE</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-10 10:23</t>
+        </is>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="4" t="inlineStr">
         <is>
           <t>Kevin Durant</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>PHI @ HOU</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C45" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D45" t="n">
+      <c r="D45" s="4" t="n">
         <v>25.5</v>
       </c>
+      <c r="E45" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G45" s="4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H45" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Durant scored 29 pts vs 25.5 line (+3.5), OVER hit by 3.5 pts. Minutes were as expected: 38 played vs L10 avg 36.1. Shooting was in line with averages: 55.6% FG (10/18, L10 avg 52.5%). Signals that called it correctly: Volume, Context, Defense, H2H, Min Trend (5/10 aligned). Counter-signals that were wrong: HR L30, HR L10, Trend. Projection model targeted 29.0 pts — actual 29 was 0.0 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Durant in this role.</t>
+        </is>
+      </c>
+      <c r="I45" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-10 10:23</t>
+        </is>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="4" t="inlineStr">
         <is>
           <t>Paul George</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B46" s="4" t="inlineStr">
         <is>
           <t>PHI @ HOU</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C46" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D46" t="n">
+      <c r="D46" s="4" t="n">
         <v>19.5</v>
       </c>
+      <c r="E46" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G46" s="4" t="n">
+        <v>-12.5</v>
+      </c>
+      <c r="H46" s="4" t="inlineStr">
+        <is>
+          <t>WIN — George scored 7 pts vs 19.5 line (-12.5), UNDER hit by 12.5 pts. George played 24 min (-9.2 vs L10 avg of 33.3) — 28% less than expected. Shooting efficiency was cold: 25.0% FG (-20.7% vs L10 avg of 45.7%). 2/8 from the field. Signals that called it correctly: Volume, HR L30, Context, Defense, Pace (5/10 aligned). Counter-signals that were wrong: HR L10, Trend, H2H. Projection model targeted 11.8 pts — actual 7 was 4.8 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms George's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I46" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-10 10:23</t>
+        </is>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="A47" s="4" t="inlineStr">
         <is>
           <t>Alperen Sengun</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>PHI @ HOU</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C47" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D47" t="n">
+      <c r="D47" s="4" t="n">
         <v>19.5</v>
       </c>
+      <c r="E47" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="n">
+        <v>-11.5</v>
+      </c>
+      <c r="H47" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Sengun scored 8 pts vs 19.5 line (-11.5), UNDER hit by 11.5 pts. Minutes were as expected: 33 played vs L10 avg 32.9. Shooting efficiency was cold: 28.6% FG (-32.2% vs L10 avg of 60.8%). 4/14 from the field. Signals that called it correctly: HR L30, Trend, Context, H2H, Pace (5/10 aligned). Counter-signals that were wrong: Volume, HR L10, Defense. Projection model targeted 14.9 pts — actual 8 was 6.9 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Sengun's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I47" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-10 10:23</t>
+        </is>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="A48" s="3" t="inlineStr">
         <is>
           <t>Amen Thompson</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B48" s="3" t="inlineStr">
         <is>
           <t>PHI @ HOU</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C48" s="3" t="inlineStr">
         <is>
           <t>LEAN UNDER</t>
         </is>
       </c>
-      <c r="D48" t="n">
+      <c r="D48" s="3" t="n">
         <v>18.5</v>
       </c>
+      <c r="E48" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Thompson scored 19 pts vs 18.5 line (+0.5), UNDER missed by 0.5 pts. Thompson played 42 min (+3.6 vs L10 avg of 38.2) — 9% more than expected. Shooting efficiency was cold: 50.0% FG (-7.8% vs L10 avg of 57.8%). 7/14 from the field. Counter-signals that proved correct: Trend, Defense, H2H, FG Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 18.7 pts — actual 19 was 0.3 pts close (wrong direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-10 10:23</t>
+        </is>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="A49" s="3" t="inlineStr">
         <is>
           <t>VJ Edgecombe</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B49" s="3" t="inlineStr">
         <is>
           <t>PHI @ HOU</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C49" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D49" t="n">
+      <c r="D49" s="3" t="n">
         <v>15.5</v>
       </c>
+      <c r="E49" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Edgecombe scored 21 pts vs 15.5 line (+5.5), UNDER missed by 5.5 pts. Edgecombe played 40 min (+4.8 vs L10 avg of 35.3) — 14% more than expected. Shooting efficiency was cold: 41.2% FG (-11.8% vs L10 avg of 53.0%). 7/17 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, Context. Signals that were wrong: Trend, Defense, Pace. Projection model targeted 8.5 pts — actual 21 was 12.5 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-10 10:23</t>
+        </is>
+      </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="A50" s="4" t="inlineStr">
         <is>
           <t>Jabari Smith Jr.</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B50" s="4" t="inlineStr">
         <is>
           <t>PHI @ HOU</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C50" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D50" t="n">
+      <c r="D50" s="4" t="n">
         <v>15.5</v>
       </c>
+      <c r="E50" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Jr. scored 19 pts vs 15.5 line (+3.5), OVER hit by 3.5 pts. Minutes were as expected: 34 played vs L10 avg 35.9. Shooting efficiency was hot: 46.7% FG (+5.0% vs L10 avg of 41.7%). 7/15 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (8/10 aligned). Counter-signals that were wrong: Pace, FG Trend. Projection model targeted 18.6 pts — actual 19 was 0.4 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Strong signal alignment (8/10) with confirmed result — this player/matchup pattern is reliable for future predictions.</t>
+        </is>
+      </c>
+      <c r="I50" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-10 10:23</t>
+        </is>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="A51" s="4" t="inlineStr">
         <is>
           <t>Kelly Oubre Jr.</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B51" s="4" t="inlineStr">
         <is>
           <t>PHI @ HOU</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C51" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D51" t="n">
+      <c r="D51" s="4" t="n">
         <v>13.5</v>
       </c>
+      <c r="E51" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G51" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H51" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Jr. scored 16 pts vs 13.5 line (+2.5), OVER hit by 2.5 pts. Minutes were as expected: 27 played vs L10 avg 28.5. Shooting efficiency was hot: 70.0% FG (+28.9% vs L10 avg of 41.1%). 7/10 from the field. Signals that called it correctly: Volume, HR L30, Context (3/10 aligned). Counter-signals that were wrong: HR L10, Trend, Defense. Projection model targeted 14.9 pts — actual 16 was 1.1 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Jr. in this role.</t>
+        </is>
+      </c>
+      <c r="I51" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-10 10:23</t>
+        </is>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="A52" s="4" t="inlineStr">
         <is>
           <t>Reed Sheppard</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B52" s="4" t="inlineStr">
         <is>
           <t>PHI @ HOU</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C52" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D52" t="n">
+      <c r="D52" s="4" t="n">
         <v>12.5</v>
       </c>
+      <c r="E52" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G52" s="4" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="H52" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Sheppard scored 6 pts vs 12.5 line (-6.5), UNDER hit by 6.5 pts. Sheppard played 19 min (-10.5 vs L10 avg of 29.1) — 36% less than expected. Shooting efficiency was cold: 28.6% FG (-17.9% vs L10 avg of 46.5%). 2/7 from the field. Signals that called it correctly: Pace, Min Trend (2/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 9.3 pts — actual 6 was 3.3 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Sheppard's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I52" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-10 10:23</t>
+        </is>
+      </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="A53" s="4" t="inlineStr">
         <is>
           <t>Tari Eason</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B53" s="4" t="inlineStr">
         <is>
           <t>PHI @ HOU</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C53" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D53" t="n">
+      <c r="D53" s="4" t="n">
         <v>9.5</v>
       </c>
+      <c r="E53" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G53" s="4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H53" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Eason scored 15 pts vs 9.5 line (+5.5), OVER hit by 5.5 pts. Eason played 27 min (+3.9 vs L10 avg of 23.3) — 17% more than expected. Shooting efficiency was hot: 50.0% FG (+11.9% vs L10 avg of 38.1%). 5/10 from the field. Signals that called it correctly: Trend, Context, Defense, H2H, FG Trend (5/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 11.2 pts — actual 15 was 3.8 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Eason's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I53" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J53" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-10 10:23</t>
+        </is>
+      </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="A54" s="4" t="inlineStr">
         <is>
           <t>Quentin Grimes</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B54" s="4" t="inlineStr">
         <is>
           <t>PHI @ HOU</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C54" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D54" t="n">
+      <c r="D54" s="4" t="n">
         <v>9.5</v>
       </c>
+      <c r="E54" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G54" s="4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H54" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Grimes scored 20 pts vs 9.5 line (+10.5), OVER hit by 10.5 pts. Minutes were as expected: 26 played vs L10 avg 27.3. Shooting was in line with averages: 43.8% FG (7/16, L10 avg 43.3%). Signals that called it correctly: Volume, HR L30, HR L10, Context, H2H (5/10 aligned). Counter-signals that were wrong: Trend, Defense, Pace. Projection model targeted 11.4 pts — actual 20 was 8.6 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Grimes's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I54" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-10 10:23</t>
+        </is>
+      </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
+      <c r="A55" s="4" t="inlineStr">
         <is>
           <t>Andre Drummond</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B55" s="4" t="inlineStr">
         <is>
           <t>PHI @ HOU</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C55" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D55" t="n">
+      <c r="D55" s="4" t="n">
         <v>6.5</v>
       </c>
+      <c r="E55" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G55" s="4" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H55" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Drummond scored 5 pts vs 6.5 line (-1.5), UNDER hit by 1.5 pts. Drummond played 30 min (+13.7 vs L10 avg of 16.3) — 84% more than expected. Shooting efficiency was hot: 100.0% FG (+57.8% vs L10 avg of 42.2%). 2/2 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (8/10 aligned). Counter-signals that were wrong: H2H, FG Trend. Projection model targeted 3.5 pts — actual 5 was 1.5 pts close (correct direction). Result classification: CLOSE_CALL. Note: Strong signal alignment (8/10) with confirmed result — this player/matchup pattern is reliable for future predictions.</t>
+        </is>
+      </c>
+      <c r="I55" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-10 10:23</t>
+        </is>
+      </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
+      <c r="A56" s="3" t="inlineStr">
         <is>
           <t>Aaron Holiday</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B56" s="3" t="inlineStr">
         <is>
           <t>PHI @ HOU</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C56" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D56" t="n">
+      <c r="D56" s="3" t="n">
         <v>5.5</v>
       </c>
+      <c r="E56" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Holiday scored 7 pts vs 5.5 line (+1.5), UNDER missed by 1.5 pts. Minutes were as expected: 14 played vs L10 avg 16.7. Shooting efficiency was hot: 60.0% FG (+14.8% vs L10 avg of 45.2%). 3/5 from the field. Counter-signals that proved correct: HR L10, Trend, Defense, H2H. Signals that were wrong: Volume, HR L30, Context. Projection model targeted 3.5 pts — actual 7 was 3.5 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I56" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-10 10:23</t>
+        </is>
+      </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
+      <c r="A57" s="4" t="inlineStr">
         <is>
           <t>Dominick Barlow</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B57" s="4" t="inlineStr">
         <is>
           <t>PHI @ HOU</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C57" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D57" t="n">
+      <c r="D57" s="4" t="n">
         <v>5.5</v>
       </c>
+      <c r="E57" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G57" s="4" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H57" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Barlow scored 2 pts vs 5.5 line (-3.5), UNDER hit by 3.5 pts. Barlow played 27 min (+5.8 vs L10 avg of 21.0) — 28% more than expected. Shooting efficiency was cold: 20.0% FG (-37.6% vs L10 avg of 57.6%). 1/5 from the field. Signals that called it correctly: Trend, Defense, Pace, Min Trend (4/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 4.1 pts — actual 2 was 2.1 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Barlow's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I57" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J57" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-10 10:23</t>
+        </is>
+      </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
+      <c r="A58" s="4" t="inlineStr">
         <is>
           <t>LeBron James</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B58" s="4" t="inlineStr">
         <is>
           <t>LAL @ GSW</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C58" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D58" t="n">
+      <c r="D58" s="4" t="n">
         <v>26.5</v>
       </c>
+      <c r="E58" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G58" s="4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>WIN — James scored 26 pts vs 26.5 line (-0.5), UNDER hit by 0.5 pts. Minutes were as expected: 32 played vs L10 avg 34.5. Shooting efficiency was hot: 64.7% FG (+11.3% vs L10 avg of 53.4%). 11/17 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (6/10 aligned). Counter-signals that were wrong: H2H, Pace, FG Trend. Projection model targeted 23.6 pts — actual 26 was 2.4 pts off (correct direction). Result classification: CLOSE_CALL. Note: Result confirms James's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I58" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-10 10:23</t>
+        </is>
+      </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
+      <c r="A59" s="4" t="inlineStr">
         <is>
           <t>Rui Hachimura</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B59" s="4" t="inlineStr">
         <is>
           <t>LAL @ GSW</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C59" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D59" t="n">
+      <c r="D59" s="4" t="n">
         <v>15.5</v>
       </c>
+      <c r="E59" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H59" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Hachimura scored 12 pts vs 15.5 line (-3.5), UNDER hit by 3.5 pts. Hachimura played 30 min (+6.5 vs L10 avg of 23.1) — 28% more than expected. Shooting efficiency was cold: 41.7% FG (-15.4% vs L10 avg of 57.1%). 5/12 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Context, Defense (6/10 aligned). Counter-signals that were wrong: Trend, H2H, Pace. Projection model targeted 11.6 pts — actual 12 was 0.4 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Hachimura in this role.</t>
+        </is>
+      </c>
+      <c r="I59" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-10 10:23</t>
+        </is>
+      </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
+      <c r="A60" s="4" t="inlineStr">
         <is>
           <t>Luke Kennard</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B60" s="4" t="inlineStr">
         <is>
           <t>LAL @ GSW</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C60" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D60" t="n">
+      <c r="D60" s="4" t="n">
         <v>14.5</v>
       </c>
+      <c r="E60" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G60" s="4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Kennard scored 14 pts vs 14.5 line (-0.5), UNDER hit by 0.5 pts. Kennard played 32 min (+7.0 vs L10 avg of 24.9) — 28% more than expected. Shooting efficiency was hot: 54.5% FG (+11.0% vs L10 avg of 43.5%). 6/11 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Context, H2H (6/10 aligned). Counter-signals that were wrong: Trend, Defense, Pace. Projection model targeted 11.1 pts — actual 14 was 2.9 pts off (correct direction). Result classification: CLOSE_CALL. Note: Result confirms Kennard's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I60" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-10 10:23</t>
+        </is>
+      </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
+      <c r="A61" s="3" t="inlineStr">
         <is>
           <t>Deandre Ayton</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B61" s="3" t="inlineStr">
         <is>
           <t>LAL @ GSW</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C61" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D61" t="n">
+      <c r="D61" s="3" t="n">
         <v>12.5</v>
       </c>
+      <c r="E61" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Ayton scored 21 pts vs 12.5 line (+8.5), UNDER missed by 8.5 pts. Ayton played 31 min (+5.3 vs L10 avg of 25.3) — 21% more than expected. Shooting efficiency was hot: 81.8% FG (+12.0% vs L10 avg of 69.8%). 9/11 from the field. Counter-signals that proved correct: Trend, Defense, Pace, FG Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 4.7 pts — actual 21 was 16.3 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I61" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-10 10:23</t>
+        </is>
+      </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
+      <c r="A62" s="3" t="inlineStr">
         <is>
           <t>Jake LaRavia</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B62" s="3" t="inlineStr">
         <is>
           <t>LAL @ GSW</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C62" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D62" t="n">
+      <c r="D62" s="3" t="n">
         <v>11.5</v>
       </c>
+      <c r="E62" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — LaRavia scored 16 pts vs 11.5 line (+4.5), UNDER missed by 4.5 pts. LaRavia played 31 min (+4.5 vs L10 avg of 26.2) — 17% more than expected. Shooting efficiency was hot: 85.7% FG (+37.7% vs L10 avg of 48.0%). 6/7 from the field. Counter-signals that proved correct: Trend, Pace, Min Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 8.0 pts — actual 16 was 8.0 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I62" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-10 10:23</t>
+        </is>
+      </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
+      <c r="A63" s="5" t="inlineStr">
         <is>
           <t>Gui Santos</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B63" s="5" t="inlineStr">
         <is>
           <t>LAL @ GSW</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C63" s="5" t="inlineStr">
         <is>
           <t>LEAN OVER</t>
         </is>
       </c>
-      <c r="D63" t="n">
+      <c r="D63" s="5" t="n">
         <v>14.5</v>
       </c>
+      <c r="E63" s="5" t="n"/>
+      <c r="F63" s="5" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="G63" s="5" t="n"/>
+      <c r="H63" s="5" t="inlineStr"/>
+      <c r="I63" s="5" t="n"/>
+      <c r="J63" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-10 10:23</t>
+        </is>
+      </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
+      <c r="A64" s="4" t="inlineStr">
         <is>
           <t>De'Anthony Melton</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B64" s="4" t="inlineStr">
         <is>
           <t>LAL @ GSW</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C64" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D64" t="n">
+      <c r="D64" s="4" t="n">
         <v>15.5</v>
       </c>
+      <c r="E64" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G64" s="4" t="n">
+        <v>-13.5</v>
+      </c>
+      <c r="H64" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Melton scored 2 pts vs 15.5 line (-13.5), UNDER hit by 13.5 pts. Melton played 15 min (-10.2 vs L10 avg of 25.1) — 41% less than expected. Shooting efficiency was cold: 20.0% FG (-14.2% vs L10 avg of 34.2%). 1/5 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (8/10 aligned). Counter-signals that were wrong: H2H, Min Trend. Projection model targeted 8.1 pts — actual 2 was 6.1 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Strong signal alignment (8/10) with confirmed result — this player/matchup pattern is reliable for future predictions.</t>
+        </is>
+      </c>
+      <c r="I64" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-10 10:23</t>
+        </is>
+      </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
+      <c r="A65" s="4" t="inlineStr">
         <is>
           <t>Brandin Podziemski</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B65" s="4" t="inlineStr">
         <is>
           <t>LAL @ GSW</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C65" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D65" t="n">
+      <c r="D65" s="4" t="n">
         <v>17.5</v>
       </c>
+      <c r="E65" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G65" s="4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H65" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Podziemski scored 17 pts vs 17.5 line (-0.5), UNDER hit by 0.5 pts. Podziemski played 24 min (-7.3 vs L10 avg of 31.3) — 23% less than expected. Shooting was in line with averages: 46.7% FG (7/15, L10 avg 50.4%). Signals that called it correctly: Volume, HR L30, Context, Defense, H2H (7/10 aligned). Counter-signals that were wrong: HR L10, Trend, FG Trend. Projection model targeted 17.0 pts — actual 17 was 0.0 pts close (correct direction). Result classification: CLOSE_CALL. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Podziemski in this role.</t>
+        </is>
+      </c>
+      <c r="I65" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-10 10:23</t>
+        </is>
+      </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
+      <c r="A66" s="4" t="inlineStr">
         <is>
           <t>Draymond Green</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B66" s="4" t="inlineStr">
         <is>
           <t>LAL @ GSW</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C66" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D66" t="n">
+      <c r="D66" s="4" t="n">
         <v>8.5</v>
+      </c>
+      <c r="E66" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G66" s="4" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="H66" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Green scored 2 pts vs 8.5 line (-6.5), UNDER hit by 6.5 pts. Green played 22 min (-7.7 vs L10 avg of 29.8) — 26% less than expected. Shooting efficiency was cold: 0.0% FG (-40.0% vs L10 avg of 40.0%). 0/1 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Context, H2H (6/10 aligned). Counter-signals that were wrong: Trend, Defense, FG Trend. Projection model targeted 7.0 pts — actual 2 was 5.0 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Green's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I66" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-10 10:23</t>
+        </is>
       </c>
     </row>
   </sheetData>
